--- a/excel-files/PASIG/MANGGAHAN ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/PASIG/MANGGAHAN ELEMENTARY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29607"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="153" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7001D5C4-C441-4848-885A-E1A189F1762A}"/>
+  <xr:revisionPtr revIDLastSave="158" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02A2ECF1-9C3E-4FF9-A830-557DB649BF69}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -5430,8 +5430,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E51:E58 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6 E61:E69 E71:E79 E81:E89 E91:E98 E59" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -13080,190 +13080,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27">
-      <c r="J120" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="121" spans="1:27">
-      <c r="J121" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="122" spans="1:27">
-      <c r="J122" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="123" spans="1:27">
-      <c r="J123" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="124" spans="1:27">
-      <c r="J124" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="125" spans="1:27">
-      <c r="J125" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="126" spans="1:27">
-      <c r="J126" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="127" spans="1:27">
-      <c r="J127" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10" ht="15"/>
-    <row r="153" spans="10:10" ht="15"/>
-    <row r="155" spans="10:10" ht="15"/>
-    <row r="156" spans="10:10" ht="15"/>
+    <row r="150" ht="15"/>
+    <row r="153" ht="15"/>
+    <row r="155" ht="15"/>
+    <row r="156" ht="15"/>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C55:C63 C65:C73 C75:C83 C85:C93 C95:C102 C104:C119 C45:C53 C5:C9 C17:C23 C25:C33 C35:C43 C11:C15" name="Textbooks"/>
@@ -13281,8 +13101,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S104:S119 M104:M119 Y104:Y119 G104:G119" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X25:X33 X35:X43 X55:X63 X65:X73 X45:X53 L104:L119 X75:X83 X85:X93 X5:X9 L25:L33 L35:L43 L55:L63 L65:L73 L45:L53 R104:R119 L75:L83 L85:L93 L5:L9 R25:R33 R35:R43 R55:R63 R65:R73 R45:R53 F104:F119 R75:R83 R85:R93 R5:R9 F25:F33 F35:F43 F55:F63 F65:F73 F45:F53 F5:F9 F75:F83 F85:F93 F95:F102 R95:R102 L95:L102 X95:X102 X104:X119 F11:F15 R11:R15 L11:L15 X11:X15 F17:F23 R17:R23 L17:L23 X17:X23" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F104:F119 F95:F102 F85:F93 F75:F83 F65:F73 F55:F63 F45:F53 F35:F43 F25:F33 F17:F23 F11:F15 F5:F9 L104:L119 L95:L102 L85:L93 L75:L83 L65:L73 L55:L63 L45:L53 L35:L43 L25:L33 L17:L23 L11:L15 L5:L9 R104:R119 R95:R102 R85:R93 R75:R83 R65:R73 R55:R63 R45:R53 R35:R43 R25:R33 R17:R23 R11:R15 R5:R9 X104:X119 X95:X102 X85:X93 X75:X83 X65:X73 X55:X63 X45:X53 X35:X43 X25:X33 X17:X23 X11:X15 X5:X9" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5:G9 M5:M9 Y5:Y9 G25:G33 G17:G23 G45:G53 G55:G63 G65:G73 G75:G83 G85:G93 G95:G102 G11:G15 S4:S102 Y11:Y102 M11:M102 G35:G43" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -21141,190 +20961,10 @@
       <c r="AA132" s="7"/>
       <c r="AB132" s="7"/>
     </row>
-    <row r="133" spans="1:28">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="1:28">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="1:28">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="1:28">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="1:28">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="1:28">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="1:28">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="1:28">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10" ht="15"/>
-    <row r="166" spans="10:10" ht="15"/>
-    <row r="168" spans="10:10" ht="15"/>
-    <row r="169" spans="10:10" ht="15"/>
+    <row r="163" ht="15"/>
+    <row r="166" ht="15"/>
+    <row r="168" ht="15"/>
+    <row r="169" ht="15"/>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C59:C69 C71:C81 C107:C114 C95:C105 C83:C93 C47:C57 C2:C7 C15:C21 C23:C33 C35:C45 C9:C13" name="Textbooks"/>
@@ -21342,8 +20982,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S107:S114 Y107:Y114 G107:G114 Y3:Y7 S3:S7 M3:M7 G3:G7 S23:S33 M23:M33 G23:G33 Y23:Y33 Y35:Y45 S35:S45 M35:M45 G35:G45 G47:G57 Y47:Y57 S47:S57 M15:M21 M59:M69 G59:G69 Y59:Y69 S59:S69 S71:S81 M71:M81 G71:G81 Y71:Y81 Y83:Y93 S83:S93 M83:M93 G83:G93 G95:G105 Y95:Y105 S95:S105 M95:M105 M107:M114 M9:M13 S9:S13 Y9:Y13 G9:G13 S15:S21 Y15:Y21 G15:G21 M47:M57" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X33 X35:X45 X59:X69 X71:X81 X47:X57 X83:X93 X95:X105 X3:X7 L23:L33 L35:L45 L59:L69 L71:L81 L47:L57 L83:L93 L95:L105 L3:L7 R23:R33 R35:R45 R59:R69 R71:R81 R47:R57 R83:R93 R95:R105 R3:R7 F23:F33 F35:F45 F59:F69 F71:F81 F47:F57 F3:F7 F83:F93 X107:X114 F107:F114 R107:R114 L107:L114 F95:F105 F9:F13 R9:R13 L9:L13 X9:X13 F15:F21 R15:R21 L15:L21 X15:X21" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F107:F114 F95:F105 F83:F93 F71:F81 F59:F69 F47:F57 F35:F45 F23:F33 F15:F21 F9:F13 F3:F7 L107:L114 L95:L105 L83:L93 L71:L81 L59:L69 L47:L57 L35:L45 L23:L33 L15:L21 L9:L13 L3:L7 R107:R114 R95:R105 R83:R93 R71:R81 R59:R69 R47:R57 R35:R45 R23:R33 R15:R21 R9:R13 R3:R7 X107:X114 X95:X105 X83:X93 X71:X81 X59:X69 X47:X57 X35:X45 X23:X33 X15:X21 X9:X13 X3:X7" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
